--- a/tabular/genus/dependo-refseqs-side-data.xlsx
+++ b/tabular/genus/dependo-refseqs-side-data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr date1904="1" showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertgifford/Projects/virus/comparative/DNA/Parvovirus-GLUE/tabular/genus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Parvovirus-GLUE/tabular/genus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856CBE9E-CAAE-954A-BC20-8CEDFD2F6076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C26763D-EAA2-BC48-B96F-B5E98FD897C6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2920" yWindow="2060" windowWidth="37540" windowHeight="20020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="860" yWindow="500" windowWidth="27940" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REFSET" sheetId="3" r:id="rId1"/>
+    <sheet name="Out" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="140001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="148">
   <si>
     <t>virus_name</t>
   </si>
@@ -436,6 +437,39 @@
   </si>
   <si>
     <t>Bos taurus</t>
+  </si>
+  <si>
+    <t>Adeno-associated virus 10</t>
+  </si>
+  <si>
+    <t>NCBI refseq</t>
+  </si>
+  <si>
+    <t>MG745677</t>
+  </si>
+  <si>
+    <t>MN794870</t>
+  </si>
+  <si>
+    <t>Feline dependoparvovirus</t>
+  </si>
+  <si>
+    <t>Felis catus</t>
+  </si>
+  <si>
+    <t>Dependo5</t>
+  </si>
+  <si>
+    <t>Desmodus rotundus dependoparvoviru</t>
+  </si>
+  <si>
+    <t>FeDPV</t>
+  </si>
+  <si>
+    <t>DrDPV</t>
+  </si>
+  <si>
+    <t>Desmodus rotundus</t>
   </si>
 </sst>
 </file>
@@ -483,7 +517,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -550,6 +584,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.24994659260841701"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1477,7 +1517,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1493,6 +1533,7 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="915">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -2753,18 +2794,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="37.5" customWidth="1"/>
-    <col min="4" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="11" width="15.5" customWidth="1"/>
-    <col min="12" max="12" width="26.83203125" customWidth="1"/>
-    <col min="13" max="13" width="20.1640625" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="37.5" customWidth="1"/>
+    <col min="5" max="9" width="18.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="13" max="13" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -2775,1354 +2816,1234 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="A2" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="M2" s="10" t="b">
-        <v>0</v>
-      </c>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="M2" s="13"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="A3" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="M3" s="10" t="b">
-        <v>0</v>
-      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="M3" s="13"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>112</v>
+      <c r="A4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="F4" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="M4" s="9" t="b">
-        <v>0</v>
+      <c r="I4" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>112</v>
+      <c r="A5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="F5" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="M5" s="9" t="b">
-        <v>0</v>
+      <c r="I5" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="E6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="G6" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="J6" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="L6" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="M6" s="9" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="G7" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="J7" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="L7" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="M7" s="9" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="J8" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="L8" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="M8" s="9" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F9" s="10" t="s">
+      <c r="A9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="M9" s="7" t="b">
-        <v>0</v>
+      <c r="I9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10" s="10" t="s">
+      <c r="A10" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H10" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="M10" s="7" t="b">
-        <v>0</v>
+      <c r="I10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F11" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="H11" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M11" s="7" t="b">
-        <v>0</v>
+      <c r="I11" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M12" s="7" t="b">
-        <v>0</v>
+      <c r="I12" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="M13" s="7" t="b">
-        <v>0</v>
+      <c r="I13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>60</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="H14" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L14" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="M14" s="7" t="b">
-        <v>0</v>
+      <c r="I14" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>12</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C15" s="7"/>
       <c r="D15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M15" s="7" t="b">
-        <v>0</v>
+      <c r="I15" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>65</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C16" s="7"/>
       <c r="D16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="H16" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M16" s="7" t="b">
-        <v>0</v>
+      <c r="I16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="D17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M17" s="7" t="b">
-        <v>0</v>
+      <c r="I17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="H18" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="M18" s="7" t="b">
-        <v>0</v>
+      <c r="I18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="H19" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M19" s="7" t="b">
-        <v>0</v>
+      <c r="I19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="H20" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M20" s="7" t="b">
-        <v>0</v>
+      <c r="I20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>71</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C21" s="7"/>
       <c r="D21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="H21" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M21" s="7" t="b">
-        <v>0</v>
+      <c r="I21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="H22" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M22" s="7" t="b">
-        <v>0</v>
+      <c r="I22" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="H23" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M23" s="7" t="b">
-        <v>0</v>
+      <c r="I23" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>54</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="H24" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M24" s="7" t="b">
-        <v>0</v>
+      <c r="I24" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>53</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C25" s="7"/>
       <c r="D25" s="7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F25" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G25" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="H25" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M25" s="7" t="b">
-        <v>0</v>
+      <c r="I25" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F26" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="H26" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="M26" s="7" t="b">
-        <v>0</v>
+      <c r="I26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F27" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G27" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="H27" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I27" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J27" s="2" t="s">
+      <c r="J27" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="K27" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="M27" s="7" t="b">
-        <v>0</v>
+      <c r="L27" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F28" s="10" t="s">
+      <c r="A28" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="H28" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="I28" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I28" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="K28" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="M28" s="7" t="b">
-        <v>0</v>
+      <c r="L28" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>90</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F29" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="H29" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L29" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="M29" s="7" t="b">
-        <v>0</v>
+      <c r="I29" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M29" s="12" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>106</v>
+      <c r="A30" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F30" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="H30" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="M30" s="7" t="b">
-        <v>0</v>
+      <c r="I30" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M30" s="12" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>81</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="C31" s="7"/>
       <c r="D31" s="7" t="s">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="F31" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="H31" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H31" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="M31" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J32" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L32" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="M32" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>127</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E33" s="10" t="s">
+      <c r="I31" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J31" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="H33" s="2" t="s">
+      <c r="K31" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="L31" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="M31" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="M33" s="7" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M32">
-    <sortCondition ref="I2:I32"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:M30">
+    <sortCondition ref="J4:J30"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -4132,4 +4053,219 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{182928F4-C6A6-7E43-90B4-5C49691E5A77}">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M2" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M3" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M4" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M5" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tabular/genus/dependo-refseqs-side-data.xlsx
+++ b/tabular/genus/dependo-refseqs-side-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Parvovirus-GLUE/tabular/genus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C26763D-EAA2-BC48-B96F-B5E98FD897C6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD9AD67-B524-2E43-A931-D031699FF969}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="500" windowWidth="27940" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REFSET" sheetId="3" r:id="rId1"/>
@@ -517,7 +517,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -532,31 +532,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDEF3A8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,18 +554,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8D379"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.24994659260841701"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1517,23 +1481,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="915">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -2452,7 +2412,368 @@
     <cellStyle name="Hyperlink" xfId="913" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <mruColors>
@@ -2470,6 +2791,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4081CC4C-296B-6B46-A372-674622A74599}" name="Table1" displayName="Table1" ref="A1:M31" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:M31" xr:uid="{B2BBDB8A-B288-A547-A854-839B6D678BF3}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{970123D4-028E-7041-BC5E-DFB9739ED989}" name="sequenceID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{11EC9726-578A-1440-9030-9028E702DA79}" name="virus_name" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{84CF87C9-914C-F144-A10E-2B6D65916845}" name="NCBI refseq" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{D745EB75-FB5E-BD4E-BA94-3A69AC41DDBE}" name="virus_full_name" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{43B9F139-5635-8944-9FCC-B81C2E54CF88}" name="host_species" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{A3E1D96A-BB64-5C4E-A32F-CAC835CE8930}" name="assign_clade" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{AAC7275D-1C5C-A04D-8D04-4E503ED75F57}" name="virus_subfamily" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{5ED37893-1F40-E54F-A51F-164A6E12863F}" name="virus_genus" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{19DA5D92-DBE3-4849-843A-73871BFAA21A}" name="assign_subclade" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{8F1D5ED3-751D-274E-8309-0E6CC8AD2DCB}" name="virus_clade_ns" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{B2F2147C-584F-504B-BBA6-5B022FA3C0DC}" name="virus_subclade_ns" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{D6FC6205-7369-F94E-8457-30BA5AFEE40C}" name="virus_clade_vp" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{FC9DBE24-4CC6-CA40-AD1D-B7CF9D439205}" name="virus_subclade_vp" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2803,1241 +3146,1241 @@
     <col min="4" max="4" width="37.5" customWidth="1"/>
     <col min="5" max="9" width="18.6640625" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="18.5" customWidth="1"/>
-    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" customWidth="1"/>
     <col min="13" max="13" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13" t="s">
+      <c r="I2" s="8"/>
+      <c r="J2" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13" t="s">
+      <c r="K2" s="8"/>
+      <c r="L2" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="M2" s="13"/>
+      <c r="M2" s="8"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13" t="s">
+      <c r="I3" s="8"/>
+      <c r="J3" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13" t="s">
+      <c r="K3" s="8"/>
+      <c r="L3" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="M3" s="13"/>
+      <c r="M3" s="8"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="8" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="8" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="8" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="M7" s="8" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="8" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" s="8" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="M10" s="8" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="F11" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="J11" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K11" s="12" t="s">
+      <c r="J11" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K11" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="L11" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M11" s="12" t="s">
+      <c r="L11" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M11" s="9" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G12" s="10" t="s">
+      <c r="F12" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K12" s="12" t="s">
+      <c r="J12" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K12" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="L12" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M12" s="12" t="s">
+      <c r="L12" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M12" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G13" s="10" t="s">
+      <c r="F13" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K13" s="4" t="s">
+      <c r="J13" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L13" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M13" s="4" t="s">
+      <c r="L13" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M13" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="8"/>
+      <c r="D14" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G14" s="10" t="s">
+      <c r="F14" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K14" s="4" t="s">
+      <c r="J14" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L14" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M14" s="4" t="s">
+      <c r="L14" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M14" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7" t="s">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G15" s="10" t="s">
+      <c r="F15" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K15" s="4" t="s">
+      <c r="J15" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L15" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M15" s="11" t="s">
+      <c r="L15" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M15" s="8" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7" t="s">
+      <c r="C16" s="8"/>
+      <c r="D16" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G16" s="10" t="s">
+      <c r="F16" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J16" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K16" s="4" t="s">
+      <c r="J16" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L16" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M16" s="11" t="s">
+      <c r="L16" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M16" s="8" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="F17" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J17" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K17" s="4" t="s">
+      <c r="J17" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L17" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M17" s="4" t="s">
+      <c r="L17" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M17" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G18" s="10" t="s">
+      <c r="F18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J18" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K18" s="4" t="s">
+      <c r="J18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L18" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M18" s="4" t="s">
+      <c r="L18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M18" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7" t="s">
+      <c r="C19" s="8"/>
+      <c r="D19" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G19" s="10" t="s">
+      <c r="F19" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J19" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K19" s="4" t="s">
+      <c r="J19" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K19" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L19" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M19" s="4" t="s">
+      <c r="L19" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M19" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G20" s="10" t="s">
+      <c r="F20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J20" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K20" s="4" t="s">
+      <c r="J20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K20" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L20" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M20" s="11" t="s">
+      <c r="L20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M20" s="8" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7" t="s">
+      <c r="C21" s="8"/>
+      <c r="D21" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G21" s="10" t="s">
+      <c r="F21" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J21" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K21" s="4" t="s">
+      <c r="J21" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K21" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L21" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M21" s="4" t="s">
+      <c r="L21" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M21" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G22" s="10" t="s">
+      <c r="F22" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J22" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K22" s="4" t="s">
+      <c r="J22" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L22" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M22" s="4" t="s">
+      <c r="L22" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M22" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="F23" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J23" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K23" s="4" t="s">
+      <c r="J23" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K23" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L23" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M23" s="4" t="s">
+      <c r="L23" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M23" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7" t="s">
+      <c r="C24" s="8"/>
+      <c r="D24" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G24" s="10" t="s">
+      <c r="F24" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="J24" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K24" s="4" t="s">
+      <c r="J24" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L24" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M24" s="4" t="s">
+      <c r="L24" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M24" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7" t="s">
+      <c r="C25" s="8"/>
+      <c r="D25" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G25" s="10" t="s">
+      <c r="F25" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G25" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="J25" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K25" s="2" t="s">
+      <c r="J25" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K25" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="L25" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M25" s="2" t="s">
+      <c r="L25" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M25" s="8" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G26" s="10" t="s">
+      <c r="F26" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="J26" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K26" s="2" t="s">
+      <c r="J26" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K26" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="L26" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M26" s="2" t="s">
+      <c r="L26" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M26" s="8" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G27" s="10" t="s">
+      <c r="F27" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="I27" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K27" s="2" t="s">
+      <c r="J27" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K27" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="L27" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M27" s="11" t="s">
+      <c r="L27" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M27" s="8" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8" t="s">
+      <c r="C28" s="9"/>
+      <c r="D28" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F28" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G28" s="10" t="s">
+      <c r="F28" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="I28" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="J28" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K28" s="2" t="s">
+      <c r="J28" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K28" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="L28" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M28" s="2" t="s">
+      <c r="L28" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M28" s="8" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7" t="s">
+      <c r="C29" s="8"/>
+      <c r="D29" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G29" s="10" t="s">
+      <c r="F29" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G29" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I29" s="12" t="s">
+      <c r="I29" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="J29" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K29" s="12" t="s">
+      <c r="J29" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K29" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="L29" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M29" s="12" t="s">
+      <c r="L29" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M29" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7" t="s">
+      <c r="C30" s="8"/>
+      <c r="D30" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G30" s="10" t="s">
+      <c r="F30" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G30" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="I30" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="J30" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K30" s="12" t="s">
+      <c r="J30" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K30" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="L30" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M30" s="12" t="s">
+      <c r="L30" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M30" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7" t="s">
+      <c r="C31" s="8"/>
+      <c r="D31" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="J31" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="K31" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="L31" s="10" t="s">
+      <c r="L31" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="M31" s="8" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4047,6 +4390,9 @@
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
@@ -4097,171 +4443,171 @@
       <c r="L1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="3" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="E2" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="K2" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M2" s="7" t="b">
+      <c r="M2" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J3" s="4" t="s">
+      <c r="I3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L3" s="4" t="s">
+      <c r="K3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M3" s="7" t="b">
+      <c r="M3" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="E4" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J4" s="4" t="s">
+      <c r="I4" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L4" s="4" t="s">
+      <c r="K4" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M4" s="7" t="b">
+      <c r="M4" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F5" s="10" t="s">
+      <c r="E5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="I5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L5" s="4" t="s">
+      <c r="K5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M5" s="7" t="b">
+      <c r="M5" s="4" t="b">
         <v>0</v>
       </c>
     </row>
